--- a/作成中事業計画書/新20261001【更新版】作成中【指定様式】事業計画書（その３）第8回フォーマット.xlsx
+++ b/作成中事業計画書/新20261001【更新版】作成中【指定様式】事業計画書（その３）第8回フォーマット.xlsx
@@ -3534,7 +3534,7 @@
     <t>約2.5〜3時間に1回（1日4〜6回）、パレットを装填し空パレットを取り出す（約3分／回）。遅番はオペレーターが兼務</t>
   </si>
   <si>
-    <t>パウチ形状が変わる品種切替時に、機内25枚のガイド幅を替える（約1.1分／枚≒28分）。月平均</t>
+    <t>形状が変わる切替時（2品種の日の半数）に機内25枚のガイド幅を替える（約28分）。予備は形状別。月平均</t>
   </si>
   <si>
     <t>株式会社トンボ飲料</t>
@@ -3553,7 +3553,7 @@
   <si>
     <t>付加価値額（営業利益＋人件費＋減価償却費）は、基準年度（2028年3月期）1,593,327,430円→1年目1,692,179,517円→2年目1,791,169,755円→3年目（2031年3月期）1,891,288,147円（基準年度比＋297,960,717円、年平均成長率5.88％）と推移する。
 （1）売上高：本装置は製袋機の能力を上げないが、供給待ちによる停止（1日約30分）の解消と土曜稼働（月2日）で年約470万袋の余地が生まれる。生産能力の不足で断った案件（年800万袋×50円）の約半分（約2億円）を受注し、価格転嫁（＋1.5％）と既存顧客の増量を加えて1年目は前年比＋4.0％（＋460百万円）とする。2年目は日勤へ戻った社員による提案型ODMの獲得、3年目はその定着で各＋4.0％とし、売上高は11,506百万円→12,943百万円となる。年＋4.0％は清涼飲料の生産者販売金額の伸び（2025年＋5.3％）を下回る保守的な水準である。
-（2）売上原価率：ODM売上比率を約10％→3年目約14.5％に高め（年＋0.30pt）、価格転嫁（＋0.05pt）と労務費の抑制（1年目＋0.07pt）で賃上げによる労務費率の上昇を吸収し、保守的に年0.25pt改善して、90.50％→89.75％とする。その他販管費は売上高比4.77％を維持し、営業利益は214百万円→330百万円となる。
+（2）売上原価率：ODM売上比率を約10％→3年目約14.5％に高め（1年目は既存の開発体制で＋1.2pt≒＋0.24pt、社員を再配置する2・3年目は各＋1.65pt≒＋0.33pt）、価格転嫁（年＋0.05pt）と労務費の抑制（1年目＋0.07pt）で賃上げによる労務費率の上昇を吸収し、保守的に年0.25pt改善して、90.50％→89.75％とする。その他販管費は売上高比4.77％を維持し、営業利益は214百万円→330百万円となる。
 （3）人件費：1人当たり年3.5％の賃上げと年3〜4名の新卒採用により、1,080百万円→1,252百万円とする（役員報酬は据え置き）。
 （4）減価償却費：既存分298,864,468円に本設備（92,000,000円・定額法10年）の9,200,000円／年を加え、308,064,468円とする。
 目標値として策定する4・5年目は、ODM比率の上昇が定着して原価率を年0.30pt改善し、付加価値額は2,008,310,651円→2,127,257,599円（年平均成長率5.95％）とする。</t>
